--- a/lorenzo-playwright-kdf/excelFramework/testcases/Referral/LSTP_Referral_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Referral/LSTP_Referral_WF001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uthalla\ORBIS PAS UKI-LZO 1\ORBIS PAS UKI-LZO\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Referral\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Referral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F81F4A-0D2A-4840-AAC3-0E5A3122877F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72065495-A92A-498C-92DA-46DEA3EAB9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45C6BE27-5324-4041-A113-6D22C593EB70}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{45C6BE27-5324-4041-A113-6D22C593EB70}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -1508,7 +1508,7 @@
         <v>81</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>82</v>
@@ -4397,4 +4397,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a4153a30-97aa-49dd-8839-66f72081522c}" enabled="1" method="Standard" siteId="{9ffff5c3-bdfa-4a9d-b595-ff68329945ef}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/lorenzo-playwright-kdf/excelFramework/testcases/Referral/LSTP_Referral_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Referral/LSTP_Referral_WF001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Referral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72065495-A92A-498C-92DA-46DEA3EAB9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639E08C5-C8A5-4243-BD67-0AE76E7E84FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{45C6BE27-5324-4041-A113-6D22C593EB70}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{45C6BE27-5324-4041-A113-6D22C593EB70}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="238">
   <si>
     <t>StepNo</t>
   </si>
@@ -763,6 +763,9 @@
   </si>
   <si>
     <t>txt_Yes</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
   </si>
 </sst>
 </file>
@@ -1962,7 +1965,7 @@
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>17</v>
       </c>
@@ -1977,7 +1980,7 @@
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="7" t="s">
-        <v>15</v>
+        <v>237</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -2103,7 +2106,7 @@
         <v>77</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>15</v>
+        <v>237</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>77</v>
